--- a/results/trace_selected25_full_temp06_seed43_answer_3b7b_results.xlsx
+++ b/results/trace_selected25_full_temp06_seed43_answer_3b7b_results.xlsx
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>64.15094339622641</v>
+        <v>68.55345911949685</v>
       </c>
       <c r="F4" t="n">
         <v>1272</v>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>55.0314465408805</v>
+        <v>57.4685534591195</v>
       </c>
       <c r="I4" t="n">
         <v>1272</v>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>68.16037735849056</v>
+        <v>68.00314465408806</v>
       </c>
       <c r="L4" t="n">
         <v>1272</v>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>77.9874213836478</v>
+        <v>78.5377358490566</v>
       </c>
       <c r="O4" t="n">
         <v>1272</v>
@@ -2382,13 +2382,13 @@
         <v>1272</v>
       </c>
       <c r="F4" t="n">
-        <v>64.15094339622641</v>
+        <v>68.55345911949685</v>
       </c>
       <c r="G4" t="n">
-        <v>55.0314465408805</v>
+        <v>57.4685534591195</v>
       </c>
       <c r="H4" t="n">
-        <v>-9.119496855345908</v>
+        <v>-11.08490566037735</v>
       </c>
     </row>
     <row r="5">
@@ -3336,13 +3336,13 @@
         <v>1272</v>
       </c>
       <c r="F4" t="n">
-        <v>68.16037735849056</v>
+        <v>68.00314465408806</v>
       </c>
       <c r="G4" t="n">
-        <v>77.9874213836478</v>
+        <v>78.5377358490566</v>
       </c>
       <c r="H4" t="n">
-        <v>9.827044025157235</v>
+        <v>10.53459119496854</v>
       </c>
     </row>
     <row r="5">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>64.15094339622641</v>
+        <v>68.55345911949685</v>
       </c>
       <c r="I10" t="n">
         <v>1272</v>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>55.0314465408805</v>
+        <v>57.4685534591195</v>
       </c>
       <c r="I11" t="n">
         <v>1272</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>68.16037735849056</v>
+        <v>68.00314465408806</v>
       </c>
       <c r="I12" t="n">
         <v>1272</v>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>77.9874213836478</v>
+        <v>78.5377358490566</v>
       </c>
       <c r="I13" t="n">
         <v>1272</v>

--- a/results/trace_selected25_full_temp06_seed43_answer_3b7b_results.xlsx
+++ b/results/trace_selected25_full_temp06_seed43_answer_3b7b_results.xlsx
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17.97945205479452</v>
+        <v>19.17808219178082</v>
       </c>
       <c r="F10" t="n">
         <v>1168</v>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>19.00684931506849</v>
+        <v>21.23287671232877</v>
       </c>
       <c r="I10" t="n">
         <v>1168</v>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>21.23287671232877</v>
+        <v>24.14383561643836</v>
       </c>
       <c r="L10" t="n">
         <v>1168</v>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>24.57191780821918</v>
+        <v>27.05479452054795</v>
       </c>
       <c r="O10" t="n">
         <v>1168</v>
@@ -2586,13 +2586,13 @@
         <v>1168</v>
       </c>
       <c r="F10" t="n">
-        <v>17.97945205479452</v>
+        <v>19.17808219178082</v>
       </c>
       <c r="G10" t="n">
-        <v>19.00684931506849</v>
+        <v>21.23287671232877</v>
       </c>
       <c r="H10" t="n">
-        <v>1.027397260273972</v>
+        <v>2.054794520547947</v>
       </c>
     </row>
     <row r="11">
@@ -3540,13 +3540,13 @@
         <v>1168</v>
       </c>
       <c r="F10" t="n">
-        <v>21.23287671232877</v>
+        <v>24.14383561643836</v>
       </c>
       <c r="G10" t="n">
-        <v>24.57191780821918</v>
+        <v>27.05479452054795</v>
       </c>
       <c r="H10" t="n">
-        <v>3.339041095890412</v>
+        <v>2.910958904109592</v>
       </c>
     </row>
     <row r="11">
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>17.97945205479452</v>
+        <v>19.17808219178082</v>
       </c>
       <c r="I34" t="n">
         <v>1168</v>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>19.00684931506849</v>
+        <v>21.23287671232877</v>
       </c>
       <c r="I35" t="n">
         <v>1168</v>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>21.23287671232877</v>
+        <v>24.14383561643836</v>
       </c>
       <c r="I36" t="n">
         <v>1168</v>
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>24.57191780821918</v>
+        <v>27.05479452054795</v>
       </c>
       <c r="I37" t="n">
         <v>1168</v>

--- a/results/trace_selected25_full_temp06_seed43_answer_3b7b_results.xlsx
+++ b/results/trace_selected25_full_temp06_seed43_answer_3b7b_results.xlsx
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>34.1371</v>
+        <v>34.1370558376</v>
       </c>
       <c r="F17" t="n">
         <v>788</v>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>40.736</v>
+        <v>40.7360406091</v>
       </c>
       <c r="I17" t="n">
         <v>788</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>43.6548</v>
+        <v>43.654822335</v>
       </c>
       <c r="L17" t="n">
         <v>788</v>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>46.7005</v>
+        <v>46.7005076142</v>
       </c>
       <c r="O17" t="n">
         <v>788</v>
@@ -2824,13 +2824,13 @@
         <v>788</v>
       </c>
       <c r="F17" t="n">
-        <v>19.79695431472081</v>
+        <v>34.1370558376</v>
       </c>
       <c r="G17" t="n">
-        <v>22.46192893401015</v>
+        <v>40.7360406091</v>
       </c>
       <c r="H17" t="n">
-        <v>2.664974619289339</v>
+        <v>6.5989847715</v>
       </c>
     </row>
     <row r="18">
@@ -3778,13 +3778,13 @@
         <v>788</v>
       </c>
       <c r="F17" t="n">
-        <v>23.60406091370558</v>
+        <v>43.654822335</v>
       </c>
       <c r="G17" t="n">
-        <v>24.87309644670051</v>
+        <v>46.7005076142</v>
       </c>
       <c r="H17" t="n">
-        <v>1.269035532994923</v>
+        <v>3.045685279200001</v>
       </c>
     </row>
     <row r="18">
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>19.79695431472081</v>
+        <v>34.1370558376</v>
       </c>
       <c r="I62" t="n">
         <v>788</v>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>22.46192893401015</v>
+        <v>40.7360406091</v>
       </c>
       <c r="I63" t="n">
         <v>788</v>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>23.60406091370558</v>
+        <v>43.654822335</v>
       </c>
       <c r="I64" t="n">
         <v>788</v>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>24.87309644670051</v>
+        <v>46.7005076142</v>
       </c>
       <c r="I65" t="n">
         <v>788</v>
